--- a/StructureDefinition-assistance-needs-ext.xlsx
+++ b/StructureDefinition-assistance-needs-ext.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://ig.opennz.org/StructureDefinition/assistance-needs-ext</t>
+    <t>https://ig.opennz.org/StructureDefinition/assistance-needs-ext</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T09:45:49+00:00</t>
+    <t>2024-06-13T01:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>FHIR New Republic (http://ig.opennz.org)</t>
+    <t>FHIR New Republic (https://ig.opennz.org)</t>
   </si>
   <si>
     <t>Description</t>
@@ -342,7 +342,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://ig.opennz.org/ValueSet/assistance-needs-vs</t>
+    <t>https://ig.opennz.org/ValueSet/assistance-needs-vs</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -676,7 +676,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.19921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.15234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-assistance-needs-ext.xlsx
+++ b/StructureDefinition-assistance-needs-ext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-13T01:01:15+00:00</t>
+    <t>2024-06-13T05:29:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-assistance-needs-ext.xlsx
+++ b/StructureDefinition-assistance-needs-ext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-13T05:29:47+00:00</t>
+    <t>2024-06-21T01:45:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-assistance-needs-ext.xlsx
+++ b/StructureDefinition-assistance-needs-ext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T01:45:26+00:00</t>
+    <t>2024-06-21T04:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
